--- a/packages/templates/files/sheet-ledger.xlsx
+++ b/packages/templates/files/sheet-ledger.xlsx
@@ -420,7 +420,7 @@
     <row r="5">
       <c r="A5" s="2">
         <f>TODAY()-30</f>
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -450,7 +450,7 @@
     <row r="6">
       <c r="A6" s="2">
         <f>A5+1</f>
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -483,7 +483,7 @@
     <row r="7">
       <c r="A7" s="2">
         <f>A5+4</f>
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
     <row r="8">
       <c r="A8" s="2">
         <f>A5+7</f>
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     <row r="9">
       <c r="A9" s="2">
         <f>A5+10</f>
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
     <row r="10">
       <c r="A10" s="2">
         <f>A5+13</f>
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
     <row r="11">
       <c r="A11" s="2">
         <f>A5+16</f>
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
     <row r="12">
       <c r="A12" s="2">
         <f>A5+19</f>
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     <row r="13">
       <c r="A13" s="2">
         <f>A5+22</f>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
     <row r="14">
       <c r="A14" s="2">
         <f>A5+25</f>
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
     <row r="15">
       <c r="A15" s="2">
         <f>A5+28</f>
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
